--- a/data/trans_dic/P37A$medicootras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicootras-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,1; 1,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,67</t>
+          <t>0,31; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,32</t>
+          <t>0,15; 1,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,42</t>
+          <t>0,25; 1,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,55</t>
+          <t>0,45; 1,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,63</t>
+          <t>0,07; 0,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,95</t>
+          <t>0,2; 0,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,77</t>
+          <t>0,13; 0,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,28</t>
+          <t>0,52; 1,43</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -862,47 +862,47 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,29</t>
+          <t>0,21; 1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,19</t>
+          <t>0,12; 1,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,58</t>
+          <t>0,22; 1,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,96</t>
+          <t>0,5; 2,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,23</t>
+          <t>0,27; 1,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,35</t>
+          <t>1,06; 2,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,32</t>
+          <t>0,47; 1,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,54</t>
+          <t>0,8; 1,78</t>
         </is>
       </c>
     </row>
@@ -944,39 +944,39 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,69</t>
+          <t>0,28; 1,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,15</t>
+          <t>0,12; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,13; 1,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,83</t>
+          <t>0,78; 2,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,99</t>
+          <t>0,2; 1,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,35</t>
+          <t>0,54; 1,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,49</t>
+          <t>0,11; 1,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,78</t>
+          <t>0,32; 1,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,33</t>
+          <t>0,31; 1,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,94</t>
+          <t>0,09; 0,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,58</t>
+          <t>0,29; 1,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,62</t>
+          <t>0,31; 1,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,91</t>
+          <t>0,7; 1,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,69</t>
+          <t>0,15; 0,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,11</t>
+          <t>0,34; 1,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,41</t>
+          <t>0,51; 1,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,44</t>
+          <t>0,62; 1,39</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,44</t>
+          <t>0,09; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,82</t>
+          <t>0,29; 0,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,45</t>
+          <t>0,1; 0,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,12</t>
+          <t>0,48; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,97</t>
+          <t>0,41; 0,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,52</t>
+          <t>1,02; 1,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,37</t>
+          <t>0,13; 0,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,84</t>
+          <t>0,45; 0,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,84</t>
+          <t>0,46; 0,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,13</t>
+          <t>0,8; 1,24</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>12480</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6932</t>
+          <t>0; 7115</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>728; 7545</t>
+          <t>726; 7166</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4400</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1278; 10626</t>
+          <t>2149; 12817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5676</t>
+          <t>0; 6175</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1012; 9184</t>
+          <t>1042; 9254</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1680; 9581</t>
+          <t>1696; 8797</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2966; 11263</t>
+          <t>3322; 12211</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>947; 8644</t>
+          <t>947; 8928</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2732; 13289</t>
+          <t>2785; 13049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1728; 10351</t>
+          <t>1738; 11145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5838; 17416</t>
+          <t>7350; 20326</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>25190</t>
         </is>
       </c>
     </row>
@@ -1858,57 +1858,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2104; 13097</t>
+          <t>2131; 12674</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1199; 12136</t>
+          <t>1197; 13920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1385; 18901</t>
+          <t>2340; 19384</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5334</t>
+          <t>0; 6979</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5337; 20206</t>
+          <t>5195; 21946</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2784; 12868</t>
+          <t>2852; 13664</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9831; 22502</t>
+          <t>11306; 26646</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6244</t>
+          <t>0; 5324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9466; 27059</t>
+          <t>9572; 27434</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6019; 20086</t>
+          <t>6069; 19931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12218; 33141</t>
+          <t>16990; 37835</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>15075</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10546</t>
+          <t>0; 10314</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 12674</t>
+          <t>0; 13179</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2187; 12833</t>
+          <t>2161; 12650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>887; 8127</t>
+          <t>947; 8996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 6357</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1003; 9242</t>
+          <t>1000; 10142</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9130</t>
+          <t>0; 9698</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3784; 17083</t>
+          <t>6343; 17927</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>980; 10827</t>
+          <t>982; 10826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2995; 15233</t>
+          <t>3002; 16369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4144; 17278</t>
+          <t>4183; 17286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7159; 22044</t>
+          <t>8661; 21941</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19578</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>844; 7962</t>
+          <t>844; 7916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1070; 14137</t>
+          <t>1058; 12980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3890; 16714</t>
+          <t>3041; 16507</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3185; 12285</t>
+          <t>3118; 11959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>980; 9786</t>
+          <t>982; 9002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3688; 16578</t>
+          <t>3029; 15524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3912; 16884</t>
+          <t>3238; 16777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7037; 20941</t>
+          <t>7836; 22130</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2851; 13618</t>
+          <t>2892; 13445</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5822; 22098</t>
+          <t>6847; 24430</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9885; 27956</t>
+          <t>10078; 28089</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12122; 29125</t>
+          <t>12981; 29335</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2907; 14457</t>
+          <t>2979; 14692</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9266; 28163</t>
+          <t>9776; 27767</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12383; 32105</t>
+          <t>12605; 31835</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12427; 32778</t>
+          <t>14427; 35185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3235; 15080</t>
+          <t>3238; 14612</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17003; 39836</t>
+          <t>17138; 38382</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13900; 34501</t>
+          <t>14526; 34650</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32107; 56453</t>
+          <t>38129; 63449</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8652; 24923</t>
+          <t>8863; 25425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30317; 58695</t>
+          <t>31271; 59397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30556; 58271</t>
+          <t>31829; 58698</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49790; 80917</t>
+          <t>57944; 89819</t>
         </is>
       </c>
     </row>
